--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -9535,7 +9535,7 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
+          <t>Jerry Jeudy (CLE)</t>
         </is>
       </c>
       <c r="C138" s="18" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C139" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
+          <t>Jonathon Brooks (CAR)</t>
         </is>
       </c>
       <c r="C140" s="16" t="inlineStr">
@@ -9590,11 +9590,11 @@
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C141" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
+          <t>Calvin Ridley (TEN)</t>
         </is>
       </c>
       <c r="C142" s="18" t="inlineStr">
@@ -9636,11 +9636,11 @@
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
+          <t>Cooper Kupp (SEA)</t>
         </is>
       </c>
       <c r="C143" s="18" t="inlineStr">
@@ -9659,11 +9659,11 @@
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C144" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C145" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C146" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9742,12 +9742,12 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C148" s="19" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C149" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
+          <t>Jordyn Tyson (NO)</t>
         </is>
       </c>
       <c r="C150" s="18" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
+          <t>Denzel Boston (CLE)</t>
         </is>
       </c>
       <c r="C151" s="18" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C153" s="16" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
+          <t>Woody Marks (HOU)</t>
         </is>
       </c>
       <c r="C154" s="16" t="inlineStr">
@@ -9912,11 +9912,11 @@
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C156" s="19" t="inlineStr">
@@ -9958,11 +9958,11 @@
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C157" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C157" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C158" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
-        </is>
-      </c>
-      <c r="C160" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
+          <t>Jalen Nailor (LV)</t>
         </is>
       </c>
       <c r="C161" s="18" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C162" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C163" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
+          <t>Zach Charbonnet (SEA)</t>
         </is>
       </c>
       <c r="C164" s="16" t="inlineStr">
@@ -10142,11 +10142,11 @@
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
+          <t>Malik Washington (MIA)</t>
         </is>
       </c>
       <c r="C166" s="18" t="inlineStr">
@@ -10188,11 +10188,11 @@
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C167" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C168" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
+          <t>Travis Hunter (JAX)</t>
         </is>
       </c>
       <c r="C170" s="18" t="inlineStr">
@@ -10280,11 +10280,11 @@
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
+          <t>Jalen Tolbert (MIA)</t>
         </is>
       </c>
       <c r="C171" s="18" t="inlineStr">
@@ -10303,11 +10303,11 @@
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
+          <t>Devaughn Vele (NO)</t>
         </is>
       </c>
       <c r="C172" s="18" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C174" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
+          <t>Germie Bernard (PIT)</t>
         </is>
       </c>
       <c r="C175" s="18" t="inlineStr">
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
+          <t>Dontayvion Wicks (PHI)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
@@ -10418,11 +10418,11 @@
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C178" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
+          <t>Ja'Kobi Lane (BAL)</t>
         </is>
       </c>
       <c r="C179" s="18" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
+          <t>DeMario Douglas (NE)</t>
         </is>
       </c>
       <c r="C180" s="18" t="inlineStr">
@@ -10510,11 +10510,11 @@
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C181" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
+          <t>Mike Washington Jr. (LV)</t>
         </is>
       </c>
       <c r="C182" s="16" t="inlineStr">
@@ -10556,11 +10556,11 @@
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C183" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
+          <t>Zachariah Branch (ATL)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
@@ -10602,11 +10602,11 @@
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C185" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
+          <t>Tank Bigsby (PHI)</t>
         </is>
       </c>
       <c r="C186" s="16" t="inlineStr">
@@ -10648,11 +10648,11 @@
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
-        </is>
-      </c>
-      <c r="C187" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
+          <t>Caleb Douglas (MIA)</t>
         </is>
       </c>
       <c r="C188" s="18" t="inlineStr">
@@ -10694,11 +10694,11 @@
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C190" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C190" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C191" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C192" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
+          <t>Ryan Flournoy (DAL)</t>
         </is>
       </c>
       <c r="C193" s="18" t="inlineStr">
@@ -10809,11 +10809,11 @@
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10823,7 +10823,7 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
+          <t>Keon Coleman (BUF)</t>
         </is>
       </c>
       <c r="C194" s="18" t="inlineStr">
@@ -10832,11 +10832,11 @@
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
+          <t>Tank Dell (HOU)</t>
         </is>
       </c>
       <c r="C195" s="18" t="inlineStr">
@@ -10855,11 +10855,11 @@
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
+          <t>Cyrus Allen (KC)</t>
         </is>
       </c>
       <c r="C196" s="18" t="inlineStr">
@@ -10878,11 +10878,11 @@
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C197" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C198" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C199" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C200" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
